--- a/testplan/WITSML 1.4.1 Certification Test Plan.xlsx
+++ b/testplan/WITSML 1.4.1 Certification Test Plan.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="165" windowWidth="15165" windowHeight="6900"/>
+    <workbookView xWindow="-15" yWindow="285" windowWidth="15165" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="1.4.1 Test Plan" sheetId="4" r:id="rId1"/>
     <sheet name="Data Model" sheetId="5" r:id="rId2"/>
     <sheet name="Tests in Progress" sheetId="8" r:id="rId3"/>
     <sheet name="Data" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="TestState">Data!$B$2:$B$9</definedName>
@@ -34,7 +35,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -43,7 +44,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.</t>
@@ -58,7 +59,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -67,7 +68,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.
@@ -83,7 +84,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -92,7 +93,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.</t>
@@ -107,7 +108,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -116,7 +117,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.</t>
@@ -131,7 +132,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -140,7 +141,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.</t>
@@ -155,7 +156,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Craig Bye:</t>
         </r>
@@ -164,7 +165,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Not an object, but must be provided in the server file.</t>
@@ -176,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="588">
   <si>
     <t>4.1.1.1 Template Rules</t>
   </si>
@@ -2628,6 +2629,306 @@
     <t>Call AddToStore for the test dataset mudLog
 Call GetFromStore for the added mudLog
 Verify the retrieved well matches the added mudLog taking into account units.</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-004 (Get ID of all Wellbores)</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-006 (Get Details for a Wellbore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use GetFromStore using SQ-004 (Get ID of all Wellbores ) 
+</t>
+  </si>
+  <si>
+    <t>Use GetFromStore using SQ-006 (Get Details for a Wellbore) for the well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server contains a well with a wellbore.
+</t>
+  </si>
+  <si>
+    <t>91b</t>
+  </si>
+  <si>
+    <t>1) Add a wellbore to the well with all elements specified as non-null values.
+2) Use GetFromStore using SQ-006 (Get Details for a Wellbore) for the well.</t>
+  </si>
+  <si>
+    <t>1) The server returns the Wellbore in question.
+2) The wellbore returned contains all elements.</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-012 (Get Data for Growing Data-object) for Trajectory</t>
+  </si>
+  <si>
+    <t>92a</t>
+  </si>
+  <si>
+    <t>92b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use SQ-012  (Get Data for Growing Data-object) for the Mudlog
+OptionsIn=’returnElements=data-only’
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use SQ-012  (Get Data for Growing Data-object) for the Trajectory.
+OptionsIn=’returnElements=data-only’
+</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-013 (Get Restricted Data Subset)</t>
+  </si>
+  <si>
+    <t>93b</t>
+  </si>
+  <si>
+    <t>A wellbore exists.</t>
+  </si>
+  <si>
+    <t>1) Add a trajectory to the wellbore with a trajectory station with the following elements set to non-null values: dTimStn, typeTrajStation, md, tvd, incl, azi, location
+2) Use SQ-013 (Get Restricted Data Subset) for the Trajectory. OptionsIn='station-location-only'</t>
+  </si>
+  <si>
+    <t>The query returns the trajectory with the Minimal header.
+The TrajectoryStation contains:
+- dTimStn, typeTrajStation, md, tvd, incl, azi, location</t>
+  </si>
+  <si>
+    <t>Server contains at least two wells with one well having a single wellbore and one well having two wellbores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Each wellbore returned contains the following elements and only these elements:
+uidWell
+uid
+nameWell
+name
+2) Confirm that the three prerequisite wellbores are contained in the results of the query.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Server supports SQ-016 (What has Changed since a specified time) for a well
+</t>
+  </si>
+  <si>
+    <t>Test functionality covered in Dataset tests.</t>
+  </si>
+  <si>
+    <t>1) The server returns the Wellbore in question.
+2) The Wellbore returned must comply with the wellbore write-schema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 AddToStore succeeds
+Step 2 returns possibly many changeLogs, but one that matches the well (uidObject and nameObject)
+              its lastChangeType == add,
+              it has no changeHistory elements
+Step 3 UpdateInStore succeeds
+Step 4 returns possibly many changeLogs, but one that matches the well
+              its lastChangeType == update,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 2's dTimLastChange
+Step 5 DeleteFromStore succeeds
+Step 6 returns possibly many changeLogs , but one that matches the well
+              its lastChangeType == delete,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 4's dTimLastChange
+</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-012 (Get Data for Growing Data-object) for Mudlog</t>
+  </si>
+  <si>
+    <t>A wellbore exists with a Trajectory containing at least one TrajectoryStation</t>
+  </si>
+  <si>
+    <t>A wellbore exists with a Mudlog containing at least one GeologyInterval and at least one Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The query returns the trajectory with  one or more trajectoryStation elements and no header.
+Each trajectoryStation contains all mandatory properties.
+</t>
+  </si>
+  <si>
+    <t>The query returns the Mudlog with one or more GeologyInterval elements and one or more Parameter elements and no header.
+Each GeologyInterval contains all mandatory properties.
+Each Parameter contains all mandatory properties.</t>
+  </si>
+  <si>
+    <t>Use SQ-013 (Get Restricted Data Subset) for the Trajectory.
+OptionsIn=’returnElements=station-location-only’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The query returns the trajectory with one or more trajectoryStation elements and no header.
+Each trajectoryStation contains the following properties:
+typeTrajStation, md
+Each trajectoryStation contains no more than the following properties:
+dTimStn, typeTrajStation, md, tvd, incl, azi, location
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Add a Well (without specifying a uid) 
+2) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange of 1 hour ago.
+3) Update the Well by changing the Field element.
+4) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from the changeLog returned in step 2.
+5) Delete the Well
+6) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from  the changeLog returned in step 4.
+</t>
+  </si>
+  <si>
+    <t>94a</t>
+  </si>
+  <si>
+    <t>94b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Server supports SQ-016 (What has Changed since a specified time) for a wellbore
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Add a Wellbore (without specifying a uid) 
+2) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange of 1 hour ago.
+3) Update the Wellbore by changing the Number element.
+4) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from the changeLog returned in step 2.
+5) Delete the Wellbore
+6) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from  the changeLog returned in step 4.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 AddToStore succeeds
+Step 2 returns possibly many changeLogs, but one that matches the wellbore (uidObject and nameObject)
+              its lastChangeType == add,
+              it has no changeHistory elements
+Step 3 UpdateInStore succeeds
+Step 4 returns possibly many changeLogs, but one that matches the wellbore
+              its lastChangeType == update,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 2's dTimLastChange
+Step 5 DeleteFromStore succeeds
+Step 6 returns possibly many changeLogs , but one that matches the wellbore
+              its lastChangeType == delete,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 4's dTimLastChange
+</t>
+  </si>
+  <si>
+    <t>94c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Server supports SQ-016 (What has Changed since a specified time) for a Trajectory
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Add a Trajectory (without specifying a uid) 
+2) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange of 1 hour ago.
+3) Update the Trajectory by changing ServiceCompany element.
+4) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from the changeLog returned in step 2.
+5) Delete the Trajectory
+6) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from  the changeLog returned in step 4.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 AddToStore succeeds
+Step 2 returns possibly many changeLogs, but one that matches the Trajectory (uidObject and nameObject)
+              its lastChangeType == add,
+              it has no changeHistory elements
+Step 3 UpdateInStore succeeds
+Step 4 returns possibly many changeLogs, but one that matches the Trajectory
+              its lastChangeType == update,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 2's dTimLastChange
+Step 5 DeleteFromStore succeeds
+Step 6 returns possibly many changeLogs , but one that matches the Trajectory
+              its lastChangeType == delete,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 4's dTimLastChange
+</t>
+  </si>
+  <si>
+    <t>94d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Server supports SQ-016 (What has Changed since a specified time) for a Log
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 AddToStore succeeds
+Step 2 returns possibly many changeLogs, but one that matches the Log (uidObject and nameObject)
+              its lastChangeType == add,
+              it has no changeHistory elements
+Step 3 UpdateInStore succeeds
+Step 4 returns possibly many changeLogs, but one that matches the Log
+              its lastChangeType == update,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 2's dTimLastChange
+Step 5 DeleteFromStore succeeds
+Step 6 returns possibly many changeLogs , but one that matches the Log
+              its lastChangeType == delete,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 4's dTimLastChange
+</t>
+  </si>
+  <si>
+    <t>94e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Server supports SQ-016 (What has Changed since a specified time) for a MudLog
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Add a MudLog (without specifying a uid) 
+2) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange of 1 hour ago.
+3) Update the MudLog by changing mudLogCompany element.
+4) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from the changeLog returned in step 2.
+5) Delete the MudLog
+6) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from  the changeLog returned in step 4.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Add a Log (without specifying a uid) 
+2) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange of 1 hour ago.
+3) Update the Log by changing serviceCompany element.
+4) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from the changeLog returned in step 2.
+5) Delete the Log
+6) Use SQ-016 (What has Changed since a specified time) with a dTimLastChange from  the changeLog returned in step 4.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 AddToStore succeeds
+Step 2 returns possibly many changeLogs, but one that matches the MudLog (uidObject and nameObject)
+              its lastChangeType == add,
+              it has no changeHistory elements
+Step 3 UpdateInStore succeeds
+Step 4 returns possibly many changeLogs, but one that matches the MudLog
+              its lastChangeType == update,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 2's dTimLastChange
+Step 5 DeleteFromStore succeeds
+Step 6 returns possibly many changeLogs , but one that matches the MudLog
+              its lastChangeType == delete,
+              it has no changeHistory elements
+              dTimLastChange &gt; than Step 4's dTimLastChange
+</t>
+  </si>
+  <si>
+    <t>92c</t>
+  </si>
+  <si>
+    <t>Verify the Server supports SQ-012 (Get Data for Growing Data-object) for Log</t>
+  </si>
+  <si>
+    <t>A wellbore exists with a time Log containing at least one row of data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use SQ-012  (Get Data for Growing Data-object) for the Log
+OptionsIn=’returnElements=data-only’
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The query returns the Log with one logData elements and no header.
+logData contains mnemonicList, unitList and at least one data element.
+The log integrity check is successful.
+</t>
   </si>
 </sst>
 </file>
@@ -2712,14 +3013,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3439,8 +3740,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:W64" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
-  <autoFilter ref="A2:W64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:W78" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="A2:W78"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Test Case ID" dataDxfId="48"/>
     <tableColumn id="2" name="Test Type" dataDxfId="47"/>
@@ -3790,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W164"/>
+  <dimension ref="A1:W178"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="3" customWidth="1"/>
@@ -6813,76 +7114,78 @@
       <c r="V59" s="14"/>
       <c r="W59" s="32"/>
     </row>
-    <row r="60" spans="1:23" ht="90" x14ac:dyDescent="0.25">
-      <c r="A60" s="44">
-        <v>85</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="G60" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H60" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
-      <c r="O60" s="8" t="s">
-        <v>378</v>
-      </c>
+    <row r="60" spans="1:23" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A60" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="B60" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="G60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="J60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="L60" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="21"/>
       <c r="P60" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q60" s="8" t="s">
-        <v>238</v>
+        <v>373</v>
+      </c>
+      <c r="Q60" s="21" t="s">
+        <v>374</v>
       </c>
       <c r="R60" s="8" t="s">
         <v>42</v>
       </c>
       <c r="S60" s="43">
-        <v>41284</v>
+        <v>41292</v>
       </c>
       <c r="T60" s="18">
         <v>41298</v>
       </c>
-      <c r="U60" s="18"/>
-      <c r="V60" s="18"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
       <c r="W60" s="32"/>
     </row>
-    <row r="61" spans="1:23" ht="105" x14ac:dyDescent="0.25">
-      <c r="A61" s="20">
-        <v>86</v>
-      </c>
-      <c r="B61" s="15" t="s">
+    <row r="61" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="A61" s="44">
+        <v>85</v>
+      </c>
+      <c r="B61" s="45" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>300</v>
+        <v>446</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="F61" s="46" t="s">
         <v>105</v>
@@ -6890,165 +7193,169 @@
       <c r="G61" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="J61" s="46" t="s">
-        <v>105</v>
-      </c>
+      <c r="H61" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46"/>
       <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
+      <c r="L61" s="46" t="s">
+        <v>105</v>
+      </c>
       <c r="M61" s="46"/>
       <c r="N61" s="46"/>
-      <c r="O61" s="49"/>
+      <c r="O61" s="8" t="s">
+        <v>378</v>
+      </c>
       <c r="P61" s="21" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="Q61" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R61" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="R61" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="S61" s="50">
-        <v>41312</v>
+      <c r="S61" s="43">
+        <v>41284</v>
       </c>
       <c r="T61" s="18">
-        <v>41326</v>
+        <v>41298</v>
       </c>
       <c r="U61" s="18"/>
       <c r="V61" s="18"/>
       <c r="W61" s="32"/>
     </row>
-    <row r="62" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="G62" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="J62" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="P62" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q62" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="R62" s="15" t="s">
+      <c r="C62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F62" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="G62" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="J62" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="K62" s="46"/>
+      <c r="L62" s="46"/>
+      <c r="M62" s="46"/>
+      <c r="N62" s="46"/>
+      <c r="O62" s="49"/>
+      <c r="P62" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q62" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R62" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="S62" s="18"/>
+      <c r="S62" s="50">
+        <v>41312</v>
+      </c>
       <c r="T62" s="18">
-        <v>41256</v>
+        <v>41326</v>
       </c>
       <c r="U62" s="18"/>
       <c r="V62" s="18"/>
       <c r="W62" s="32"/>
     </row>
-    <row r="63" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B63" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>326</v>
+        <v>242</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>300</v>
+        <v>448</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>109</v>
+        <v>447</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G63" s="17"/>
+      <c r="G63" s="17" t="s">
+        <v>105</v>
+      </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="J63" s="17"/>
+      <c r="J63" s="17" t="s">
+        <v>105</v>
+      </c>
       <c r="K63" s="17"/>
-      <c r="L63" s="17" t="s">
-        <v>105</v>
-      </c>
+      <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
-      <c r="O63" s="16"/>
+      <c r="O63" s="16" t="s">
+        <v>241</v>
+      </c>
       <c r="P63" s="26" t="s">
-        <v>386</v>
+        <v>284</v>
       </c>
       <c r="Q63" s="16" t="s">
-        <v>387</v>
+        <v>243</v>
       </c>
       <c r="R63" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="S63" s="18">
-        <v>41111</v>
-      </c>
+      <c r="S63" s="18"/>
       <c r="T63" s="18">
-        <v>41354</v>
+        <v>41256</v>
       </c>
       <c r="U63" s="18"/>
       <c r="V63" s="18"/>
       <c r="W63" s="32"/>
     </row>
-    <row r="64" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>300</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>449</v>
+        <v>109</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G64" s="17" t="s">
-        <v>105</v>
-      </c>
+      <c r="G64" s="17"/>
       <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
+      <c r="I64" s="17" t="s">
+        <v>105</v>
+      </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17" t="s">
@@ -7058,16 +7365,16 @@
       <c r="N64" s="17"/>
       <c r="O64" s="16"/>
       <c r="P64" s="26" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="Q64" s="16" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="R64" s="15" t="s">
         <v>42</v>
       </c>
       <c r="S64" s="18">
-        <v>41340</v>
+        <v>41111</v>
       </c>
       <c r="T64" s="18">
         <v>41354</v>
@@ -7076,59 +7383,775 @@
       <c r="V64" s="18"/>
       <c r="W64" s="32"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="19"/>
-      <c r="C65" s="11" t="s">
+    <row r="65" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="A65" s="20">
+        <v>89</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="16"/>
+      <c r="P65" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q65" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="R65" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="S65" s="18">
+        <v>41340</v>
+      </c>
+      <c r="T65" s="18">
+        <v>41354</v>
+      </c>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="32"/>
+    </row>
+    <row r="66" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="A66" s="20">
+        <v>90</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>534</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="26" t="s">
+        <v>552</v>
+      </c>
+      <c r="P66" s="26" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q66" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="R66" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S66" s="14">
+        <v>41591</v>
+      </c>
+      <c r="T66" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="32"/>
+    </row>
+    <row r="67" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="20">
+        <v>91</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E67" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="26" t="s">
+        <v>538</v>
+      </c>
+      <c r="P67" s="26" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q67" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="R67" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S67" s="14">
+        <v>41591</v>
+      </c>
+      <c r="T67" s="14">
+        <v>41647</v>
+      </c>
+      <c r="U67" s="18"/>
+      <c r="V67" s="18"/>
+      <c r="W67" s="32"/>
+    </row>
+    <row r="68" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="A68" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="P68" s="26" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q68" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="R68" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="S68" s="14"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="18"/>
+      <c r="W68" s="32" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="A69" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>542</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N69" s="13"/>
+      <c r="O69" s="26" t="s">
+        <v>559</v>
+      </c>
+      <c r="P69" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q69" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="R69" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S69" s="14">
+        <v>41626</v>
+      </c>
+      <c r="T69" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="32"/>
+    </row>
+    <row r="70" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="A70" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>558</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="O70" s="26" t="s">
+        <v>560</v>
+      </c>
+      <c r="P70" s="26" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q70" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="R70" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S70" s="14">
+        <v>41626</v>
+      </c>
+      <c r="T70" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U70" s="18"/>
+      <c r="V70" s="18"/>
+      <c r="W70" s="32"/>
+    </row>
+    <row r="71" spans="1:23" s="11" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>584</v>
+      </c>
+      <c r="D71" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="26" t="s">
+        <v>585</v>
+      </c>
+      <c r="P71" s="26" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q71" s="26" t="s">
+        <v>587</v>
+      </c>
+      <c r="R71" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S71" s="14">
+        <v>41626</v>
+      </c>
+      <c r="T71" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U71" s="18"/>
+      <c r="V71" s="18"/>
+      <c r="W71" s="32"/>
+    </row>
+    <row r="72" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="A72" s="20">
+        <v>93</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>547</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N72" s="13"/>
+      <c r="O72" s="26" t="s">
+        <v>559</v>
+      </c>
+      <c r="P72" s="26" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q72" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="R72" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S72" s="14">
+        <v>41626</v>
+      </c>
+      <c r="T72" s="14">
+        <v>41696</v>
+      </c>
+      <c r="U72" s="18"/>
+      <c r="V72" s="18"/>
+      <c r="W72" s="32"/>
+    </row>
+    <row r="73" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="A73" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>547</v>
+      </c>
+      <c r="D73" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N73" s="13"/>
+      <c r="O73" s="26" t="s">
+        <v>549</v>
+      </c>
+      <c r="P73" s="26" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q73" s="26" t="s">
+        <v>551</v>
+      </c>
+      <c r="R73" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="S73" s="14"/>
+      <c r="T73" s="14"/>
+      <c r="U73" s="18"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="32"/>
+    </row>
+    <row r="74" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+      <c r="A74" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26" t="s">
+        <v>565</v>
+      </c>
+      <c r="Q74" s="26" t="s">
+        <v>557</v>
+      </c>
+      <c r="R74" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S74" s="14">
+        <v>41598</v>
+      </c>
+      <c r="T74" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U74" s="18"/>
+      <c r="V74" s="18"/>
+      <c r="W74" s="32"/>
+    </row>
+    <row r="75" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+      <c r="A75" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>568</v>
+      </c>
+      <c r="D75" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q75" s="26" t="s">
+        <v>570</v>
+      </c>
+      <c r="R75" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S75" s="14">
+        <v>41647</v>
+      </c>
+      <c r="T75" s="14"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="32"/>
+    </row>
+    <row r="76" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+      <c r="A76" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N76" s="13"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q76" s="26" t="s">
+        <v>574</v>
+      </c>
+      <c r="R76" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S76" s="14">
+        <v>41647</v>
+      </c>
+      <c r="T76" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U76" s="18"/>
+      <c r="V76" s="18"/>
+      <c r="W76" s="32"/>
+    </row>
+    <row r="77" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+      <c r="A77" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="26" t="s">
+        <v>576</v>
+      </c>
+      <c r="D77" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q77" s="26" t="s">
+        <v>577</v>
+      </c>
+      <c r="R77" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S77" s="14">
+        <v>41647</v>
+      </c>
+      <c r="T77" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U77" s="18"/>
+      <c r="V77" s="18"/>
+      <c r="W77" s="32"/>
+    </row>
+    <row r="78" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+      <c r="A78" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q78" s="26" t="s">
+        <v>582</v>
+      </c>
+      <c r="R78" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S78" s="14">
+        <v>41647</v>
+      </c>
+      <c r="T78" s="14">
+        <v>41689</v>
+      </c>
+      <c r="U78" s="18"/>
+      <c r="V78" s="18"/>
+      <c r="W78" s="32"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A79" s="19"/>
+      <c r="C79" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="C66" s="11" t="s">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+      <c r="C80" s="11" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="7"/>
@@ -7381,20 +8404,62 @@
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F1:N1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R63:R64">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R64:R65">
       <formula1>TestState</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B34">
       <formula1>TestType</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R66:R78 R3:R63">
       <formula1>TestState</formula1>
     </dataValidation>
   </dataValidations>
@@ -12988,6 +14053,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
@@ -12998,6 +14072,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100620A2F6665993049BF983589C8264F5B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="286d57dfc87ccb6cf0b61c1cdcf1d2ea">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns3="94fbc3ec-7e0b-4269-ada3-e3a1cb3d52d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cc6847f50fe6aa5c07c4cc0a7ce94457" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3/fields"/>
@@ -13069,32 +14152,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C93BB28-581C-41CB-9157-7C837CA54C1E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="94fbc3ec-7e0b-4269-ada3-e3a1cb3d52d8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D69C45C-ECA8-4B6E-8260-EDE2C5CA81F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62EB2FB-3789-452B-8A9E-C8264D97F637}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13110,12 +14192,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D69C45C-ECA8-4B6E-8260-EDE2C5CA81F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>